--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -3548,7 +3548,7 @@
         <v>136556155</v>
       </c>
       <c r="B26" t="n">
-        <v>58446</v>
+        <v>58448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>136378876</v>
       </c>
       <c r="B39" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2107,7 +2107,7 @@
         <v>136036391</v>
       </c>
       <c r="B14" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2107,7 +2107,7 @@
         <v>136036391</v>
       </c>
       <c r="B14" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2107,7 +2107,7 @@
         <v>136036391</v>
       </c>
       <c r="B14" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2135,11 +2135,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2107,7 +2107,7 @@
         <v>136036391</v>
       </c>
       <c r="B14" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2107,7 +2107,7 @@
         <v>136036391</v>
       </c>
       <c r="B14" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2107,7 +2107,7 @@
         <v>136036391</v>
       </c>
       <c r="B14" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 58174-2022 artfynd.xlsx
+++ b/artfynd/A 58174-2022 artfynd.xlsx
@@ -2107,7 +2107,7 @@
         <v>136036391</v>
       </c>
       <c r="B14" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
